--- a/seating_generator/examples/places.xlsx
+++ b/seating_generator/examples/places.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\chgk\dchr\seating\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.berezanskiy\chgk\git\games_features\seating_generator\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBDD9273-B1A7-447A-AFCC-48E79866DA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD647019-A3A4-4CE2-9971-271F6B409801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{CE70294A-DA95-4BF4-AAC9-15F0C364B3AE}"/>
+    <workbookView xWindow="4483" yWindow="3369" windowWidth="16320" windowHeight="13765" xr2:uid="{CE70294A-DA95-4BF4-AAC9-15F0C364B3AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,12 +34,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="3">
   <si>
     <t>X</t>
   </si>
   <si>
     <t>O</t>
+  </si>
+  <si>
+    <t>Эврика</t>
   </si>
 </sst>
 </file>
@@ -414,11 +415,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E538C4B-9DA0-43B3-B765-A7F3A21BA015}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -436,7 +437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -456,7 +457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -476,7 +477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -496,7 +497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -516,7 +517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -536,7 +537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -556,7 +557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -576,7 +577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -596,7 +597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -616,7 +617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -636,7 +637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -656,7 +657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -676,7 +677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -696,7 +697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -716,7 +717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>0</v>
       </c>
